--- a/artfynd/A 9324-2026 artfynd.xlsx
+++ b/artfynd/A 9324-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,79 +675,70 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124872838</v>
+        <v>124872861</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åkersveden, Gstr</t>
+          <t>Oxtjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566559</v>
+        <v>566237</v>
       </c>
       <c r="R2" t="n">
-        <v>6751530</v>
+        <v>6751633</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Gävleborg</t>
+          <t>Dalarna</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Ockelbo</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Gästrikland</t>
+          <t>Dalarna</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Ockelbo</t>
+          <t>Svartnäs</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -757,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:16</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,6 +782,244 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124872838</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Åkersveden, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>566559</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6751530</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124872946</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Åkersveden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>566449</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6751396</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Svartnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
